--- a/artfynd/A 35959-2025 artfynd.xlsx
+++ b/artfynd/A 35959-2025 artfynd.xlsx
@@ -1443,32 +1443,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127779820</v>
+        <v>127779776</v>
       </c>
       <c r="B9" t="n">
-        <v>98471</v>
+        <v>79020</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>221952</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1478,13 +1478,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>568153</v>
+        <v>568133</v>
       </c>
       <c r="R9" t="n">
-        <v>7084763</v>
+        <v>7084737</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1513,7 +1513,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>16:02</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1523,7 +1523,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>16:02</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1550,10 +1550,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127779640</v>
+        <v>127779820</v>
       </c>
       <c r="B10" t="n">
-        <v>97327</v>
+        <v>98471</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1561,21 +1561,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>221945</v>
+        <v>221952</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1585,10 +1585,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>568161</v>
+        <v>568153</v>
       </c>
       <c r="R10" t="n">
-        <v>7084751</v>
+        <v>7084763</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1620,7 +1620,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>15:54</t>
+          <t>16:02</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1630,7 +1630,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>15:54</t>
+          <t>16:02</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1645,44 +1645,44 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127779776</v>
+        <v>127779640</v>
       </c>
       <c r="B11" t="n">
-        <v>79020</v>
+        <v>97327</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1692,13 +1692,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>568133</v>
+        <v>568161</v>
       </c>
       <c r="R11" t="n">
-        <v>7084737</v>
+        <v>7084751</v>
       </c>
       <c r="S11" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1727,7 +1727,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1737,7 +1737,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1752,12 +1752,12 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>

--- a/artfynd/A 35959-2025 artfynd.xlsx
+++ b/artfynd/A 35959-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127779385</v>
       </c>
       <c r="B2" t="n">
-        <v>92622</v>
+        <v>92628</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1008,7 +1008,7 @@
         <v>127779879</v>
       </c>
       <c r="B5" t="n">
-        <v>98367</v>
+        <v>98373</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1339,7 +1339,7 @@
         <v>127779510</v>
       </c>
       <c r="B8" t="n">
-        <v>92622</v>
+        <v>92628</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1553,7 +1553,7 @@
         <v>127779820</v>
       </c>
       <c r="B10" t="n">
-        <v>98471</v>
+        <v>98477</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1660,7 +1660,7 @@
         <v>127779640</v>
       </c>
       <c r="B11" t="n">
-        <v>97327</v>
+        <v>97333</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 35959-2025 artfynd.xlsx
+++ b/artfynd/A 35959-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127779385</v>
       </c>
       <c r="B2" t="n">
-        <v>92628</v>
+        <v>92631</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>127779519</v>
       </c>
       <c r="B3" t="n">
-        <v>78778</v>
+        <v>78781</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -892,7 +892,7 @@
         <v>127779399</v>
       </c>
       <c r="B4" t="n">
-        <v>57823</v>
+        <v>57826</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1008,7 +1008,7 @@
         <v>127779879</v>
       </c>
       <c r="B5" t="n">
-        <v>98373</v>
+        <v>98376</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1115,7 +1115,7 @@
         <v>127779704</v>
       </c>
       <c r="B6" t="n">
-        <v>82861</v>
+        <v>82864</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1222,7 +1222,7 @@
         <v>127779342</v>
       </c>
       <c r="B7" t="n">
-        <v>57663</v>
+        <v>57666</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1339,7 +1339,7 @@
         <v>127779510</v>
       </c>
       <c r="B8" t="n">
-        <v>92628</v>
+        <v>92631</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1446,7 +1446,7 @@
         <v>127779776</v>
       </c>
       <c r="B9" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1553,7 +1553,7 @@
         <v>127779820</v>
       </c>
       <c r="B10" t="n">
-        <v>98477</v>
+        <v>98480</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1660,7 +1660,7 @@
         <v>127779640</v>
       </c>
       <c r="B11" t="n">
-        <v>97333</v>
+        <v>97336</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 35959-2025 artfynd.xlsx
+++ b/artfynd/A 35959-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127779385</v>
       </c>
       <c r="B2" t="n">
-        <v>92631</v>
+        <v>92639</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>127779519</v>
       </c>
       <c r="B3" t="n">
-        <v>78781</v>
+        <v>78787</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -892,7 +892,7 @@
         <v>127779399</v>
       </c>
       <c r="B4" t="n">
-        <v>57826</v>
+        <v>57832</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1008,7 +1008,7 @@
         <v>127779879</v>
       </c>
       <c r="B5" t="n">
-        <v>98376</v>
+        <v>98384</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1115,7 +1115,7 @@
         <v>127779704</v>
       </c>
       <c r="B6" t="n">
-        <v>82864</v>
+        <v>82870</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1222,7 +1222,7 @@
         <v>127779342</v>
       </c>
       <c r="B7" t="n">
-        <v>57666</v>
+        <v>57672</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1339,7 +1339,7 @@
         <v>127779510</v>
       </c>
       <c r="B8" t="n">
-        <v>92631</v>
+        <v>92639</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1446,7 +1446,7 @@
         <v>127779776</v>
       </c>
       <c r="B9" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1553,7 +1553,7 @@
         <v>127779820</v>
       </c>
       <c r="B10" t="n">
-        <v>98480</v>
+        <v>98488</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1660,7 +1660,7 @@
         <v>127779640</v>
       </c>
       <c r="B11" t="n">
-        <v>97336</v>
+        <v>97344</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 35959-2025 artfynd.xlsx
+++ b/artfynd/A 35959-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127779385</v>
       </c>
       <c r="B2" t="n">
-        <v>92639</v>
+        <v>92640</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1008,7 +1008,7 @@
         <v>127779879</v>
       </c>
       <c r="B5" t="n">
-        <v>98384</v>
+        <v>98385</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1339,7 +1339,7 @@
         <v>127779510</v>
       </c>
       <c r="B8" t="n">
-        <v>92639</v>
+        <v>92640</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1443,32 +1443,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127779776</v>
+        <v>127779820</v>
       </c>
       <c r="B9" t="n">
-        <v>79029</v>
+        <v>98489</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>221952</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1478,13 +1478,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>568133</v>
+        <v>568153</v>
       </c>
       <c r="R9" t="n">
-        <v>7084737</v>
+        <v>7084763</v>
       </c>
       <c r="S9" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1513,7 +1513,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>16:02</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1523,7 +1523,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>16:02</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1550,10 +1550,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127779820</v>
+        <v>127779640</v>
       </c>
       <c r="B10" t="n">
-        <v>98488</v>
+        <v>97345</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1561,21 +1561,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>221952</v>
+        <v>221945</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1585,10 +1585,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>568153</v>
+        <v>568161</v>
       </c>
       <c r="R10" t="n">
-        <v>7084763</v>
+        <v>7084751</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1620,7 +1620,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>16:02</t>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1630,7 +1630,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>16:02</t>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1645,44 +1645,44 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127779640</v>
+        <v>127779776</v>
       </c>
       <c r="B11" t="n">
-        <v>97344</v>
+        <v>79029</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1692,13 +1692,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>568161</v>
+        <v>568133</v>
       </c>
       <c r="R11" t="n">
-        <v>7084751</v>
+        <v>7084737</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1727,7 +1727,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>15:54</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1737,7 +1737,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>15:54</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1752,12 +1752,12 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>

--- a/artfynd/A 35959-2025 artfynd.xlsx
+++ b/artfynd/A 35959-2025 artfynd.xlsx
@@ -1443,32 +1443,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127779820</v>
+        <v>127779776</v>
       </c>
       <c r="B9" t="n">
-        <v>98489</v>
+        <v>79029</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>221952</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1478,13 +1478,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>568153</v>
+        <v>568133</v>
       </c>
       <c r="R9" t="n">
-        <v>7084763</v>
+        <v>7084737</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1513,7 +1513,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>16:02</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1523,7 +1523,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>16:02</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1550,10 +1550,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127779640</v>
+        <v>127779820</v>
       </c>
       <c r="B10" t="n">
-        <v>97345</v>
+        <v>98489</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1561,21 +1561,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>221945</v>
+        <v>221952</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1585,10 +1585,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>568161</v>
+        <v>568153</v>
       </c>
       <c r="R10" t="n">
-        <v>7084751</v>
+        <v>7084763</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1620,7 +1620,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>15:54</t>
+          <t>16:02</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1630,7 +1630,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>15:54</t>
+          <t>16:02</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1645,44 +1645,44 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127779776</v>
+        <v>127779640</v>
       </c>
       <c r="B11" t="n">
-        <v>79029</v>
+        <v>97345</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1692,13 +1692,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>568133</v>
+        <v>568161</v>
       </c>
       <c r="R11" t="n">
-        <v>7084737</v>
+        <v>7084751</v>
       </c>
       <c r="S11" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1727,7 +1727,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1737,7 +1737,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1752,12 +1752,12 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>

--- a/artfynd/A 35959-2025 artfynd.xlsx
+++ b/artfynd/A 35959-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127779385</v>
       </c>
       <c r="B2" t="n">
-        <v>92640</v>
+        <v>92641</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1008,7 +1008,7 @@
         <v>127779879</v>
       </c>
       <c r="B5" t="n">
-        <v>98385</v>
+        <v>98386</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1339,7 +1339,7 @@
         <v>127779510</v>
       </c>
       <c r="B8" t="n">
-        <v>92640</v>
+        <v>92641</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1553,7 +1553,7 @@
         <v>127779820</v>
       </c>
       <c r="B10" t="n">
-        <v>98489</v>
+        <v>98490</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1660,7 +1660,7 @@
         <v>127779640</v>
       </c>
       <c r="B11" t="n">
-        <v>97345</v>
+        <v>97346</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 35959-2025 artfynd.xlsx
+++ b/artfynd/A 35959-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127779385</v>
       </c>
       <c r="B2" t="n">
-        <v>92641</v>
+        <v>92642</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1008,7 +1008,7 @@
         <v>127779879</v>
       </c>
       <c r="B5" t="n">
-        <v>98386</v>
+        <v>98387</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1339,7 +1339,7 @@
         <v>127779510</v>
       </c>
       <c r="B8" t="n">
-        <v>92641</v>
+        <v>92642</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1553,7 +1553,7 @@
         <v>127779820</v>
       </c>
       <c r="B10" t="n">
-        <v>98490</v>
+        <v>98491</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1660,7 +1660,7 @@
         <v>127779640</v>
       </c>
       <c r="B11" t="n">
-        <v>97346</v>
+        <v>97347</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 35959-2025 artfynd.xlsx
+++ b/artfynd/A 35959-2025 artfynd.xlsx
@@ -1550,10 +1550,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127779820</v>
+        <v>127779640</v>
       </c>
       <c r="B10" t="n">
-        <v>98491</v>
+        <v>97347</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1561,21 +1561,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>221952</v>
+        <v>221945</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1585,10 +1585,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>568153</v>
+        <v>568161</v>
       </c>
       <c r="R10" t="n">
-        <v>7084763</v>
+        <v>7084751</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1620,7 +1620,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>16:02</t>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1630,7 +1630,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>16:02</t>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1645,22 +1645,22 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127779640</v>
+        <v>127779820</v>
       </c>
       <c r="B11" t="n">
-        <v>97347</v>
+        <v>98491</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1668,21 +1668,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>221945</v>
+        <v>221952</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1692,10 +1692,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>568161</v>
+        <v>568153</v>
       </c>
       <c r="R11" t="n">
-        <v>7084751</v>
+        <v>7084763</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1727,7 +1727,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>15:54</t>
+          <t>16:02</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1737,7 +1737,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>15:54</t>
+          <t>16:02</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1752,12 +1752,12 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>

--- a/artfynd/A 35959-2025 artfynd.xlsx
+++ b/artfynd/A 35959-2025 artfynd.xlsx
@@ -1443,32 +1443,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127779776</v>
+        <v>127779820</v>
       </c>
       <c r="B9" t="n">
-        <v>79029</v>
+        <v>98491</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>221952</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1478,13 +1478,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>568133</v>
+        <v>568153</v>
       </c>
       <c r="R9" t="n">
-        <v>7084737</v>
+        <v>7084763</v>
       </c>
       <c r="S9" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1513,7 +1513,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>16:02</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1523,7 +1523,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>16:02</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1657,32 +1657,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127779820</v>
+        <v>127779776</v>
       </c>
       <c r="B11" t="n">
-        <v>98491</v>
+        <v>79029</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>221952</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1692,13 +1692,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>568153</v>
+        <v>568133</v>
       </c>
       <c r="R11" t="n">
-        <v>7084763</v>
+        <v>7084737</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1727,7 +1727,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>16:02</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1737,7 +1737,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>16:02</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AD11" t="b">

--- a/artfynd/A 35959-2025 artfynd.xlsx
+++ b/artfynd/A 35959-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127779385</v>
       </c>
       <c r="B2" t="n">
-        <v>92642</v>
+        <v>92650</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>127779519</v>
       </c>
       <c r="B3" t="n">
-        <v>78787</v>
+        <v>78790</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -892,7 +892,7 @@
         <v>127779399</v>
       </c>
       <c r="B4" t="n">
-        <v>57832</v>
+        <v>57833</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1008,7 +1008,7 @@
         <v>127779879</v>
       </c>
       <c r="B5" t="n">
-        <v>98387</v>
+        <v>98395</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1115,7 +1115,7 @@
         <v>127779704</v>
       </c>
       <c r="B6" t="n">
-        <v>82870</v>
+        <v>82873</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1222,7 +1222,7 @@
         <v>127779342</v>
       </c>
       <c r="B7" t="n">
-        <v>57672</v>
+        <v>57673</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1339,7 +1339,7 @@
         <v>127779510</v>
       </c>
       <c r="B8" t="n">
-        <v>92642</v>
+        <v>92650</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1443,32 +1443,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127779820</v>
+        <v>127779776</v>
       </c>
       <c r="B9" t="n">
-        <v>98491</v>
+        <v>79032</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>221952</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1478,13 +1478,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>568153</v>
+        <v>568133</v>
       </c>
       <c r="R9" t="n">
-        <v>7084763</v>
+        <v>7084737</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1513,7 +1513,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>16:02</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1523,7 +1523,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>16:02</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1550,10 +1550,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127779640</v>
+        <v>127779820</v>
       </c>
       <c r="B10" t="n">
-        <v>97347</v>
+        <v>98499</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1561,21 +1561,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>221945</v>
+        <v>221952</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1585,10 +1585,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>568161</v>
+        <v>568153</v>
       </c>
       <c r="R10" t="n">
-        <v>7084751</v>
+        <v>7084763</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1620,7 +1620,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>15:54</t>
+          <t>16:02</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1630,7 +1630,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>15:54</t>
+          <t>16:02</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1645,44 +1645,44 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127779776</v>
+        <v>127779640</v>
       </c>
       <c r="B11" t="n">
-        <v>79029</v>
+        <v>97355</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1692,13 +1692,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>568133</v>
+        <v>568161</v>
       </c>
       <c r="R11" t="n">
-        <v>7084737</v>
+        <v>7084751</v>
       </c>
       <c r="S11" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1727,7 +1727,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1737,7 +1737,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1752,12 +1752,12 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>

--- a/artfynd/A 35959-2025 artfynd.xlsx
+++ b/artfynd/A 35959-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127779385</v>
       </c>
       <c r="B2" t="n">
-        <v>92650</v>
+        <v>92742</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>127779519</v>
       </c>
       <c r="B3" t="n">
-        <v>78790</v>
+        <v>78840</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -892,7 +892,7 @@
         <v>127779399</v>
       </c>
       <c r="B4" t="n">
-        <v>57833</v>
+        <v>57845</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1008,7 +1008,7 @@
         <v>127779879</v>
       </c>
       <c r="B5" t="n">
-        <v>98395</v>
+        <v>98488</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1115,7 +1115,7 @@
         <v>127779704</v>
       </c>
       <c r="B6" t="n">
-        <v>82873</v>
+        <v>82942</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1222,7 +1222,7 @@
         <v>127779342</v>
       </c>
       <c r="B7" t="n">
-        <v>57673</v>
+        <v>57685</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1339,7 +1339,7 @@
         <v>127779510</v>
       </c>
       <c r="B8" t="n">
-        <v>92650</v>
+        <v>92742</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1446,7 +1446,7 @@
         <v>127779776</v>
       </c>
       <c r="B9" t="n">
-        <v>79032</v>
+        <v>79083</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1553,7 +1553,7 @@
         <v>127779820</v>
       </c>
       <c r="B10" t="n">
-        <v>98499</v>
+        <v>98592</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1660,7 +1660,7 @@
         <v>127779640</v>
       </c>
       <c r="B11" t="n">
-        <v>97355</v>
+        <v>97448</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 35959-2025 artfynd.xlsx
+++ b/artfynd/A 35959-2025 artfynd.xlsx
@@ -1443,32 +1443,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127779776</v>
+        <v>127779640</v>
       </c>
       <c r="B9" t="n">
-        <v>79083</v>
+        <v>97448</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1478,13 +1478,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>568133</v>
+        <v>568161</v>
       </c>
       <c r="R9" t="n">
-        <v>7084737</v>
+        <v>7084751</v>
       </c>
       <c r="S9" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1513,7 +1513,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1523,7 +1523,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1538,44 +1538,44 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127779820</v>
+        <v>127779776</v>
       </c>
       <c r="B10" t="n">
-        <v>98592</v>
+        <v>79083</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>221952</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1585,13 +1585,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>568153</v>
+        <v>568133</v>
       </c>
       <c r="R10" t="n">
-        <v>7084763</v>
+        <v>7084737</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1620,7 +1620,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>16:02</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1630,7 +1630,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>16:02</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1657,10 +1657,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127779640</v>
+        <v>127779820</v>
       </c>
       <c r="B11" t="n">
-        <v>97448</v>
+        <v>98592</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1668,21 +1668,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>221945</v>
+        <v>221952</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1692,10 +1692,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>568161</v>
+        <v>568153</v>
       </c>
       <c r="R11" t="n">
-        <v>7084751</v>
+        <v>7084763</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1727,7 +1727,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>15:54</t>
+          <t>16:02</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1737,7 +1737,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>15:54</t>
+          <t>16:02</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1752,12 +1752,12 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>

--- a/artfynd/A 35959-2025 artfynd.xlsx
+++ b/artfynd/A 35959-2025 artfynd.xlsx
@@ -675,32 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>127779385</v>
+        <v>127779704</v>
       </c>
       <c r="B2" t="n">
-        <v>92742</v>
+        <v>83173</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4364</v>
+        <v>1312</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>568338</v>
+        <v>568161</v>
       </c>
       <c r="R2" t="n">
-        <v>7084750</v>
+        <v>7084754</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -745,7 +745,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>15:41</t>
+          <t>15:55</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>15:41</t>
+          <t>15:55</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127779519</v>
+        <v>127779385</v>
       </c>
       <c r="B3" t="n">
-        <v>78840</v>
+        <v>93197</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -793,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6446</v>
+        <v>4364</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>568279</v>
+        <v>568338</v>
       </c>
       <c r="R3" t="n">
-        <v>7084741</v>
+        <v>7084750</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -852,7 +852,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>15:46</t>
+          <t>15:41</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -862,7 +862,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>15:46</t>
+          <t>15:41</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -889,10 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127779399</v>
+        <v>127779510</v>
       </c>
       <c r="B4" t="n">
-        <v>57845</v>
+        <v>93197</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -900,46 +900,37 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103021</v>
+        <v>4364</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Grubbmyrlokarna, Grubbmyrlokarna, Ång</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>568337</v>
+        <v>568283</v>
       </c>
       <c r="R4" t="n">
-        <v>7084751</v>
+        <v>7084744</v>
       </c>
       <c r="S4" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -968,7 +959,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>15:42</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -978,7 +969,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>15:42</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1005,32 +996,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127779879</v>
+        <v>127779776</v>
       </c>
       <c r="B5" t="n">
-        <v>98488</v>
+        <v>79327</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>219790</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1040,13 +1031,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>568163</v>
+        <v>568133</v>
       </c>
       <c r="R5" t="n">
-        <v>7084797</v>
+        <v>7084737</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1075,7 +1066,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>16:05</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1085,7 +1076,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>16:05</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1112,10 +1103,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127779704</v>
+        <v>127779519</v>
       </c>
       <c r="B6" t="n">
-        <v>82942</v>
+        <v>79084</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1123,21 +1114,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1312</v>
+        <v>6446</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1147,10 +1138,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>568161</v>
+        <v>568279</v>
       </c>
       <c r="R6" t="n">
-        <v>7084754</v>
+        <v>7084741</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1182,7 +1173,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>15:55</t>
+          <t>15:46</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1192,7 +1183,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>15:55</t>
+          <t>15:46</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1222,7 +1213,7 @@
         <v>127779342</v>
       </c>
       <c r="B7" t="n">
-        <v>57685</v>
+        <v>57953</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1336,48 +1327,57 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127779510</v>
+        <v>127779399</v>
       </c>
       <c r="B8" t="n">
-        <v>92742</v>
+        <v>58114</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>4364</v>
+        <v>103021</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Grubbmyrlokarna, Grubbmyrlokarna, Ång</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>568283</v>
+        <v>568337</v>
       </c>
       <c r="R8" t="n">
-        <v>7084744</v>
+        <v>7084751</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1406,7 +1406,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>15:42</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1416,7 +1416,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>15:42</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1443,10 +1443,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127779640</v>
+        <v>127779879</v>
       </c>
       <c r="B9" t="n">
-        <v>97448</v>
+        <v>99035</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1454,21 +1454,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>221945</v>
+        <v>219790</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1478,10 +1478,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>568161</v>
+        <v>568163</v>
       </c>
       <c r="R9" t="n">
-        <v>7084751</v>
+        <v>7084797</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1513,7 +1513,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>15:54</t>
+          <t>16:05</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1523,7 +1523,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>15:54</t>
+          <t>16:05</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1538,44 +1538,44 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127779776</v>
+        <v>127779640</v>
       </c>
       <c r="B10" t="n">
-        <v>79083</v>
+        <v>97983</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1585,13 +1585,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>568133</v>
+        <v>568161</v>
       </c>
       <c r="R10" t="n">
-        <v>7084737</v>
+        <v>7084751</v>
       </c>
       <c r="S10" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1620,7 +1620,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1630,7 +1630,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1645,12 +1645,12 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
@@ -1660,7 +1660,7 @@
         <v>127779820</v>
       </c>
       <c r="B11" t="n">
-        <v>98592</v>
+        <v>99140</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 35959-2025 artfynd.xlsx
+++ b/artfynd/A 35959-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY11"/>
+  <dimension ref="A1:AZ11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -779,6 +784,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127779704</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -886,6 +896,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127779385</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -993,6 +1008,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127779510</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1100,6 +1120,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127779776</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1207,6 +1232,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127779519</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1324,6 +1354,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127779342</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1440,6 +1475,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127779399</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1547,6 +1587,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127779879</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1654,6 +1699,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127779640</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1761,8 +1811,25 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127779820</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>